--- a/docs/試験項目書兼結果報告書/試験項目書兼結果報告書_フォーマット.xlsx
+++ b/docs/試験項目書兼結果報告書/試験項目書兼結果報告書_フォーマット.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ryota\git\development-SEcourse-DroneInventorySystem\docs\試験項目書兼結果報告書\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ryota\git\development-PGcourse-DroneInventorySystem\docs\試験項目書兼結果報告書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67011455-CCF4-40AF-AB74-D32DA9AE3A10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B52664E0-4F4E-4218-A386-6CC1A2EB6947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{94E1F5D5-5A75-8F40-A2A1-CC833EFCF558}"/>
   </bookViews>
   <sheets>
     <sheet name="試験項目" sheetId="13" r:id="rId1"/>
     <sheet name="エビデンス" sheetId="12" r:id="rId2"/>
-    <sheet name="→不具合報告→" sheetId="15" r:id="rId3"/>
+    <sheet name="不具合報告→" sheetId="15" r:id="rId3"/>
     <sheet name="不具合報告" sheetId="1" r:id="rId4"/>
     <sheet name="障害ID_001" sheetId="14" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">エビデンス!$A$1:$AX$176</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">試験項目!$A$1:$Z$20</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">試験項目!$A$1:$U$12</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">不具合報告!$A$1:$K$24</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="59">
   <si>
     <t>システム名</t>
     <phoneticPr fontId="1"/>
@@ -130,16 +130,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>試験内容</t>
-    <rPh sb="0" eb="2">
-      <t>シケン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ナイヨウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>試験条件</t>
     <rPh sb="0" eb="2">
       <t>シケン</t>
@@ -171,16 +161,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>試験手順</t>
-    <rPh sb="0" eb="2">
-      <t>シケン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>テジュン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>判定
 １回目</t>
     <rPh sb="0" eb="2">
@@ -221,37 +201,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>①springbootを実行
-②ブラウザより　http://localhost:8080/login　を実行</t>
-    <rPh sb="12" eb="14">
-      <t>ジッコウ</t>
-    </rPh>
-    <rPh sb="52" eb="54">
-      <t>ジッコウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>①ログイン画面からログイン成功
-②メニューバーより「在庫センター情報」を押下</t>
-    <rPh sb="5" eb="7">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>セイコウ</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>ザイコ</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>オウカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>設計書の画面イメージ通りに色、ボタン、データが表示されていること。</t>
     <rPh sb="0" eb="3">
       <t>セッケイショ</t>
@@ -267,87 +216,6 @@
     </rPh>
     <rPh sb="23" eb="25">
       <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>初期表示（画面）</t>
-    <rPh sb="0" eb="4">
-      <t>ショキヒョウジ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ガメン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>画面表示時のレイアウト・表示内容を確認</t>
-    <rPh sb="0" eb="2">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="2" eb="5">
-      <t>ヒョウジジ</t>
-    </rPh>
-    <rPh sb="12" eb="16">
-      <t>ヒョウジナイヨウ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>カクニン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>初期表示（ログ）</t>
-    <rPh sb="0" eb="4">
-      <t>ショキヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>画面表示時のログ出力内容を確認</t>
-    <rPh sb="0" eb="2">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="2" eb="5">
-      <t>ヒョウジジ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>シュツリョク</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ナイヨウ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>カクニン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>初期表示（データ）</t>
-    <rPh sb="0" eb="4">
-      <t>ショキヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>画面表示時のデータ出力内容を確認</t>
-    <rPh sb="0" eb="2">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ジ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>シュツリョク</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ナイヨウ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>カクニン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -387,41 +255,6 @@
     </rPh>
     <rPh sb="83" eb="85">
       <t>ショウジュン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>【データ準備】
-稼働状況ステータス、削除フラグが「0」「1」が混在するレコードを用意
-【試験手順】
-①springbootを実行
-②ブラウザより　http://localhost:8080/login　を実行</t>
-    <rPh sb="4" eb="6">
-      <t>ジュンビ</t>
-    </rPh>
-    <rPh sb="8" eb="12">
-      <t>カドウジョウキョウ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>コンザイ</t>
-    </rPh>
-    <rPh sb="40" eb="42">
-      <t>ヨウイ</t>
-    </rPh>
-    <rPh sb="45" eb="47">
-      <t>シケン</t>
-    </rPh>
-    <rPh sb="47" eb="49">
-      <t>テジュン</t>
-    </rPh>
-    <rPh sb="63" eb="65">
-      <t>ジッコウ</t>
-    </rPh>
-    <rPh sb="103" eb="105">
-      <t>ジッコウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -737,6 +570,115 @@
     </rPh>
     <rPh sb="66" eb="68">
       <t>シュツリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>在庫センター情報画面初期表示</t>
+    <rPh sb="0" eb="2">
+      <t>ザイコ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="10" eb="14">
+      <t>ショキヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画面レイアウト・表示内容を確認</t>
+    <rPh sb="0" eb="2">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="8" eb="12">
+      <t>ヒョウジナイヨウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ログ出力内容を確認</t>
+    <rPh sb="2" eb="4">
+      <t>シュツリョク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データ出力内容を確認</t>
+    <rPh sb="3" eb="5">
+      <t>シュツリョク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>試験観点</t>
+    <rPh sb="0" eb="2">
+      <t>シケン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カンテン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>①ログイン画面からログイン成功
+②メニューバーより「在庫センター情報」を押下
+＜試験データ＞
+在庫センター情報テーブルに下記条件を登録
+「稼働状況ステータス」、「削除フラグ」の値「0」、「1」が混在するレコードを用意</t>
+    <rPh sb="5" eb="7">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>セイコウ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ザイコ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>シケン</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>ザイコ</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="61" eb="63">
+      <t>カキ</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>ジョウケン</t>
+    </rPh>
+    <rPh sb="66" eb="68">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="89" eb="90">
+      <t>アタイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -856,7 +798,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -1022,13 +964,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1164,91 +1117,121 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="14" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1257,16 +1240,22 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2046,16 +2035,16 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>40821</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>136071</xdr:rowOff>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>219076</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>39</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>209550</xdr:rowOff>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>142876</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2070,8 +2059,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="688521" y="3107871"/>
-          <a:ext cx="12065454" cy="1559379"/>
+          <a:off x="9591675" y="3933826"/>
+          <a:ext cx="942975" cy="171450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2114,14 +2103,14 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>176893</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>136072</xdr:rowOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>219075</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>29</xdr:col>
       <xdr:colOff>200025</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>108857</xdr:rowOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2136,8 +2125,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2443843" y="7565572"/>
-          <a:ext cx="7147832" cy="3192235"/>
+          <a:off x="2377168" y="9382125"/>
+          <a:ext cx="6938282" cy="419100"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2171,6 +2160,188 @@
         <a:p>
           <a:pPr algn="l"/>
           <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>219075</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>42</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="吹き出し: 折線 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F8770C83-679C-790B-2971-849E6E309D7F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11144250" y="2695575"/>
+          <a:ext cx="2152650" cy="1028700"/>
+        </a:xfrm>
+        <a:prstGeom prst="borderCallout2">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>削除フラグ＝</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>1</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>のレコード</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>39</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="吹き出し: 折線 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3BF679A3-8971-4D67-B425-CB269BAA2041}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10134600" y="8210550"/>
+          <a:ext cx="2152650" cy="1028700"/>
+        </a:xfrm>
+        <a:prstGeom prst="borderCallout2">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>削除フラグ＝</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>1</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>のレコードが表示されている</a:t>
+          </a:r>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -2476,615 +2647,424 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C00E766C-EA4C-E14A-AA5A-CA0A9C83E992}">
-  <dimension ref="A1:Y19"/>
+  <dimension ref="A1:S16"/>
   <sheetFormatPr defaultColWidth="3.6640625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="2.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="27.33203125" style="1" customWidth="1"/>
     <col min="4" max="4" width="30" style="1" customWidth="1"/>
-    <col min="5" max="5" width="32.21875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="32.33203125" style="1" customWidth="1"/>
     <col min="6" max="6" width="13.88671875" style="1" customWidth="1"/>
     <col min="7" max="7" width="14.88671875" style="1" customWidth="1"/>
     <col min="8" max="16" width="3.6640625" style="1"/>
     <col min="17" max="17" width="7.5546875" style="1" customWidth="1"/>
-    <col min="18" max="18" width="9.21875" style="1" customWidth="1"/>
-    <col min="19" max="19" width="3.6640625" style="1" customWidth="1"/>
-    <col min="20" max="20" width="3.6640625" style="1"/>
-    <col min="21" max="21" width="5.44140625" style="1" customWidth="1"/>
-    <col min="22" max="22" width="6.33203125" style="1" customWidth="1"/>
-    <col min="23" max="23" width="10.109375" style="1" customWidth="1"/>
-    <col min="24" max="24" width="9.21875" style="1" customWidth="1"/>
-    <col min="25" max="25" width="8.44140625" style="1" customWidth="1"/>
-    <col min="26" max="16384" width="3.6640625" style="1"/>
+    <col min="18" max="18" width="9.33203125" style="1" customWidth="1"/>
+    <col min="19" max="19" width="11.33203125" style="1" customWidth="1"/>
+    <col min="20" max="20" width="5.44140625" style="1" customWidth="1"/>
+    <col min="21" max="21" width="6.33203125" style="1" customWidth="1"/>
+    <col min="22" max="22" width="10.109375" style="1" customWidth="1"/>
+    <col min="23" max="23" width="9.33203125" style="1" customWidth="1"/>
+    <col min="24" max="24" width="8.44140625" style="1" customWidth="1"/>
+    <col min="25" max="16384" width="3.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="57" t="s">
+    <row r="1" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="59"/>
-      <c r="H1" s="54" t="s">
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
-      <c r="K1" s="54"/>
-      <c r="L1" s="54"/>
-      <c r="M1" s="55" t="s">
+      <c r="H1" s="46"/>
+      <c r="I1" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="N1" s="55"/>
-      <c r="O1" s="55"/>
-      <c r="P1" s="55"/>
-      <c r="Q1" s="55"/>
-      <c r="R1" s="55"/>
-      <c r="S1" s="55"/>
-      <c r="T1" s="66" t="s">
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="56"/>
+      <c r="P1" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="U1" s="66"/>
-      <c r="V1" s="66"/>
-      <c r="W1" s="67" t="s">
-        <v>39</v>
-      </c>
-      <c r="X1" s="67"/>
-    </row>
-    <row r="2" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="60"/>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="54" t="s">
+      <c r="Q1" s="54"/>
+      <c r="R1" s="54"/>
+      <c r="S1" s="47" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="63"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="54"/>
-      <c r="L2" s="54"/>
-      <c r="M2" s="55" t="s">
+      <c r="H2" s="46"/>
+      <c r="I2" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="N2" s="55"/>
-      <c r="O2" s="55"/>
-      <c r="P2" s="55"/>
-      <c r="Q2" s="55"/>
-      <c r="R2" s="55"/>
-      <c r="S2" s="55"/>
-      <c r="T2" s="66"/>
-      <c r="U2" s="66"/>
-      <c r="V2" s="66"/>
-      <c r="W2" s="67"/>
-      <c r="X2" s="67"/>
-    </row>
-    <row r="3" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="60"/>
-      <c r="B3" s="61"/>
-      <c r="C3" s="61"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="54" t="s">
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="56"/>
+      <c r="N2" s="56"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="54"/>
+      <c r="Q2" s="54"/>
+      <c r="R2" s="54"/>
+      <c r="S2" s="48"/>
+    </row>
+    <row r="3" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="63"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="54"/>
-      <c r="J3" s="54"/>
-      <c r="K3" s="54"/>
-      <c r="L3" s="54"/>
-      <c r="M3" s="56" t="s">
+      <c r="H3" s="46"/>
+      <c r="I3" s="55" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" s="55"/>
+      <c r="K3" s="55"/>
+      <c r="L3" s="55"/>
+      <c r="M3" s="55"/>
+      <c r="N3" s="55"/>
+      <c r="O3" s="55"/>
+      <c r="P3" s="54" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q3" s="54"/>
+      <c r="R3" s="54"/>
+      <c r="S3" s="49">
+        <v>45700</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="66"/>
+      <c r="B4" s="67"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="46"/>
+      <c r="I4" s="55" t="s">
         <v>16</v>
       </c>
-      <c r="N3" s="56"/>
-      <c r="O3" s="56"/>
-      <c r="P3" s="56"/>
-      <c r="Q3" s="56"/>
-      <c r="R3" s="56"/>
-      <c r="S3" s="56"/>
-      <c r="T3" s="66" t="s">
-        <v>7</v>
-      </c>
-      <c r="U3" s="66"/>
-      <c r="V3" s="66"/>
-      <c r="W3" s="68">
-        <v>45700</v>
-      </c>
-      <c r="X3" s="69"/>
-    </row>
-    <row r="4" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="63"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="I4" s="54"/>
-      <c r="J4" s="54"/>
-      <c r="K4" s="54"/>
-      <c r="L4" s="54"/>
-      <c r="M4" s="56" t="s">
+      <c r="J4" s="55"/>
+      <c r="K4" s="55"/>
+      <c r="L4" s="55"/>
+      <c r="M4" s="55"/>
+      <c r="N4" s="55"/>
+      <c r="O4" s="55"/>
+      <c r="P4" s="54"/>
+      <c r="Q4" s="54"/>
+      <c r="R4" s="54"/>
+      <c r="S4" s="50"/>
+    </row>
+    <row r="5" spans="1:19" s="7" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="72" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="73"/>
+      <c r="C5" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="74" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="74"/>
+      <c r="H5" s="74"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="74"/>
+      <c r="K5" s="74"/>
+      <c r="L5" s="74"/>
+      <c r="M5" s="72" t="s">
+        <v>25</v>
+      </c>
+      <c r="N5" s="73"/>
+      <c r="O5" s="74" t="s">
         <v>17</v>
       </c>
-      <c r="N4" s="56"/>
-      <c r="O4" s="56"/>
-      <c r="P4" s="56"/>
-      <c r="Q4" s="56"/>
-      <c r="R4" s="56"/>
-      <c r="S4" s="56"/>
-      <c r="T4" s="66"/>
-      <c r="U4" s="66"/>
-      <c r="V4" s="66"/>
-      <c r="W4" s="69"/>
-      <c r="X4" s="69"/>
-    </row>
-    <row r="5" spans="1:25" s="7" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="45" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="46"/>
-      <c r="C5" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="53" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" s="53"/>
-      <c r="H5" s="53"/>
-      <c r="I5" s="53"/>
-      <c r="J5" s="53"/>
-      <c r="K5" s="53"/>
-      <c r="L5" s="53"/>
-      <c r="M5" s="53" t="s">
+      <c r="P5" s="74"/>
+      <c r="Q5" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="N5" s="53"/>
-      <c r="O5" s="53"/>
-      <c r="P5" s="53"/>
-      <c r="Q5" s="53"/>
-      <c r="R5" s="53"/>
-      <c r="S5" s="45" t="s">
-        <v>36</v>
-      </c>
-      <c r="T5" s="46"/>
-      <c r="U5" s="53" t="s">
+      <c r="R5" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="V5" s="53"/>
-      <c r="W5" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="X5" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="Y5" s="10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25" s="7" customFormat="1" ht="69" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="8">
+      <c r="S5" s="10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" s="7" customFormat="1" ht="69" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="60">
         <f>ROW(A6)-5</f>
         <v>1</v>
       </c>
       <c r="B6" s="8">
         <v>1</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>26</v>
+      <c r="C6" s="57" t="s">
+        <v>53</v>
       </c>
       <c r="D6" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" s="57" t="s">
+        <v>58</v>
+      </c>
+      <c r="F6" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="51"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="51"/>
+      <c r="J6" s="51"/>
+      <c r="K6" s="51"/>
+      <c r="L6" s="51"/>
+      <c r="M6" s="69" t="s">
+        <v>28</v>
+      </c>
+      <c r="N6" s="70"/>
+      <c r="O6" s="71" t="s">
+        <v>23</v>
+      </c>
+      <c r="P6" s="71"/>
+      <c r="Q6" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" s="47" t="s">
-        <v>25</v>
-      </c>
-      <c r="G6" s="47"/>
-      <c r="H6" s="47"/>
-      <c r="I6" s="47"/>
-      <c r="J6" s="47"/>
-      <c r="K6" s="47"/>
-      <c r="L6" s="47"/>
-      <c r="M6" s="47" t="s">
-        <v>23</v>
-      </c>
-      <c r="N6" s="47"/>
-      <c r="O6" s="47"/>
-      <c r="P6" s="47"/>
-      <c r="Q6" s="47"/>
-      <c r="R6" s="47"/>
-      <c r="S6" s="48" t="s">
-        <v>39</v>
-      </c>
-      <c r="T6" s="49"/>
-      <c r="U6" s="50" t="s">
-        <v>34</v>
-      </c>
-      <c r="V6" s="50"/>
-      <c r="W6" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="X6" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y6" s="11" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25" s="7" customFormat="1" ht="93.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="8">
-        <v>1</v>
-      </c>
+      <c r="R6" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="S6" s="11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" s="7" customFormat="1" ht="93.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="61"/>
       <c r="B7" s="8">
         <v>2</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="58"/>
+      <c r="D7" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E7" s="58"/>
+      <c r="F7" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G7" s="51"/>
+      <c r="H7" s="51"/>
+      <c r="I7" s="51"/>
+      <c r="J7" s="51"/>
+      <c r="K7" s="51"/>
+      <c r="L7" s="51"/>
+      <c r="M7" s="69" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="N7" s="70"/>
+      <c r="O7" s="71" t="s">
+        <v>23</v>
+      </c>
+      <c r="P7" s="71"/>
+      <c r="Q7" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="R7" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="S7" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F7" s="47" t="s">
-        <v>63</v>
-      </c>
-      <c r="G7" s="47"/>
-      <c r="H7" s="47"/>
-      <c r="I7" s="47"/>
-      <c r="J7" s="47"/>
-      <c r="K7" s="47"/>
-      <c r="L7" s="47"/>
-      <c r="M7" s="47" t="s">
-        <v>23</v>
-      </c>
-      <c r="N7" s="47"/>
-      <c r="O7" s="47"/>
-      <c r="P7" s="47"/>
-      <c r="Q7" s="47"/>
-      <c r="R7" s="47"/>
-      <c r="S7" s="48" t="s">
-        <v>39</v>
-      </c>
-      <c r="T7" s="49"/>
-      <c r="U7" s="50" t="s">
-        <v>34</v>
-      </c>
-      <c r="V7" s="50"/>
-      <c r="W7" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="X7" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y7" s="11" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" s="7" customFormat="1" ht="143.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="8">
-        <v>1</v>
-      </c>
+    </row>
+    <row r="8" spans="1:19" s="7" customFormat="1" ht="143.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="62"/>
       <c r="B8" s="8">
         <v>3</v>
       </c>
-      <c r="C8" s="8" t="s">
-        <v>30</v>
-      </c>
+      <c r="C8" s="59"/>
       <c r="D8" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" s="59"/>
+      <c r="F8" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="51"/>
+      <c r="H8" s="51"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="51"/>
+      <c r="K8" s="51"/>
+      <c r="L8" s="51"/>
+      <c r="M8" s="69" t="s">
+        <v>28</v>
+      </c>
+      <c r="N8" s="70"/>
+      <c r="O8" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="G8" s="47"/>
-      <c r="H8" s="47"/>
-      <c r="I8" s="47"/>
-      <c r="J8" s="47"/>
-      <c r="K8" s="47"/>
-      <c r="L8" s="47"/>
-      <c r="M8" s="47" t="s">
-        <v>33</v>
-      </c>
-      <c r="N8" s="47"/>
-      <c r="O8" s="47"/>
-      <c r="P8" s="47"/>
-      <c r="Q8" s="47"/>
-      <c r="R8" s="47"/>
-      <c r="S8" s="48" t="s">
-        <v>39</v>
-      </c>
-      <c r="T8" s="49"/>
-      <c r="U8" s="50" t="s">
-        <v>35</v>
-      </c>
-      <c r="V8" s="50"/>
-      <c r="W8" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="X8" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y8" s="11" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.4">
+      <c r="P8" s="71"/>
+      <c r="Q8" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="R8" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="S8" s="11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.4">
       <c r="A9" s="8"/>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
-      <c r="F9" s="47"/>
-      <c r="G9" s="47"/>
-      <c r="H9" s="47"/>
-      <c r="I9" s="47"/>
-      <c r="J9" s="47"/>
-      <c r="K9" s="47"/>
-      <c r="L9" s="47"/>
-      <c r="M9" s="47"/>
-      <c r="N9" s="47"/>
-      <c r="O9" s="47"/>
-      <c r="P9" s="47"/>
-      <c r="Q9" s="47"/>
-      <c r="R9" s="47"/>
-      <c r="S9" s="51"/>
-      <c r="T9" s="52"/>
-      <c r="U9" s="47"/>
-      <c r="V9" s="47"/>
-      <c r="W9" s="14"/>
-      <c r="X9" s="14"/>
-      <c r="Y9" s="8"/>
-    </row>
-    <row r="10" spans="1:25" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.4">
+      <c r="F9" s="51"/>
+      <c r="G9" s="51"/>
+      <c r="H9" s="51"/>
+      <c r="I9" s="51"/>
+      <c r="J9" s="51"/>
+      <c r="K9" s="51"/>
+      <c r="L9" s="51"/>
+      <c r="M9" s="52"/>
+      <c r="N9" s="53"/>
+      <c r="O9" s="51"/>
+      <c r="P9" s="51"/>
+      <c r="Q9" s="14"/>
+      <c r="R9" s="14"/>
+      <c r="S9" s="8"/>
+    </row>
+    <row r="10" spans="1:19" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.4">
       <c r="A10" s="8"/>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
-      <c r="F10" s="47"/>
-      <c r="G10" s="47"/>
-      <c r="H10" s="47"/>
-      <c r="I10" s="47"/>
-      <c r="J10" s="47"/>
-      <c r="K10" s="47"/>
-      <c r="L10" s="47"/>
-      <c r="M10" s="47"/>
-      <c r="N10" s="47"/>
-      <c r="O10" s="47"/>
-      <c r="P10" s="47"/>
-      <c r="Q10" s="47"/>
-      <c r="R10" s="47"/>
-      <c r="S10" s="51"/>
-      <c r="T10" s="52"/>
-      <c r="U10" s="47"/>
-      <c r="V10" s="47"/>
-      <c r="W10" s="14"/>
-      <c r="X10" s="14"/>
-      <c r="Y10" s="8"/>
-    </row>
-    <row r="11" spans="1:25" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.4">
+      <c r="F10" s="51"/>
+      <c r="G10" s="51"/>
+      <c r="H10" s="51"/>
+      <c r="I10" s="51"/>
+      <c r="J10" s="51"/>
+      <c r="K10" s="51"/>
+      <c r="L10" s="51"/>
+      <c r="M10" s="52"/>
+      <c r="N10" s="53"/>
+      <c r="O10" s="51"/>
+      <c r="P10" s="51"/>
+      <c r="Q10" s="14"/>
+      <c r="R10" s="14"/>
+      <c r="S10" s="8"/>
+    </row>
+    <row r="11" spans="1:19" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.4">
       <c r="A11" s="8"/>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
-      <c r="F11" s="47"/>
-      <c r="G11" s="47"/>
-      <c r="H11" s="47"/>
-      <c r="I11" s="47"/>
-      <c r="J11" s="47"/>
-      <c r="K11" s="47"/>
-      <c r="L11" s="47"/>
-      <c r="M11" s="47"/>
-      <c r="N11" s="47"/>
-      <c r="O11" s="47"/>
-      <c r="P11" s="47"/>
-      <c r="Q11" s="47"/>
-      <c r="R11" s="47"/>
-      <c r="S11" s="51"/>
-      <c r="T11" s="52"/>
-      <c r="U11" s="47"/>
-      <c r="V11" s="47"/>
-      <c r="W11" s="14"/>
-      <c r="X11" s="14"/>
-      <c r="Y11" s="8"/>
-    </row>
-    <row r="12" spans="1:25" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.4">
+      <c r="F11" s="51"/>
+      <c r="G11" s="51"/>
+      <c r="H11" s="51"/>
+      <c r="I11" s="51"/>
+      <c r="J11" s="51"/>
+      <c r="K11" s="51"/>
+      <c r="L11" s="51"/>
+      <c r="M11" s="52"/>
+      <c r="N11" s="53"/>
+      <c r="O11" s="51"/>
+      <c r="P11" s="51"/>
+      <c r="Q11" s="14"/>
+      <c r="R11" s="14"/>
+      <c r="S11" s="8"/>
+    </row>
+    <row r="12" spans="1:19" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.4">
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
-      <c r="F12" s="47"/>
-      <c r="G12" s="47"/>
-      <c r="H12" s="47"/>
-      <c r="I12" s="47"/>
-      <c r="J12" s="47"/>
-      <c r="K12" s="47"/>
-      <c r="L12" s="47"/>
-      <c r="M12" s="47"/>
-      <c r="N12" s="47"/>
-      <c r="O12" s="47"/>
-      <c r="P12" s="47"/>
-      <c r="Q12" s="47"/>
-      <c r="R12" s="47"/>
-      <c r="S12" s="51"/>
-      <c r="T12" s="52"/>
-      <c r="U12" s="47"/>
-      <c r="V12" s="47"/>
-      <c r="W12" s="14"/>
-      <c r="X12" s="14"/>
-      <c r="Y12" s="8"/>
-    </row>
-    <row r="13" spans="1:25" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.4">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="47"/>
-      <c r="G13" s="47"/>
-      <c r="H13" s="47"/>
-      <c r="I13" s="47"/>
-      <c r="J13" s="47"/>
-      <c r="K13" s="47"/>
-      <c r="L13" s="47"/>
-      <c r="M13" s="47"/>
-      <c r="N13" s="47"/>
-      <c r="O13" s="47"/>
-      <c r="P13" s="47"/>
-      <c r="Q13" s="47"/>
-      <c r="R13" s="47"/>
-      <c r="S13" s="51"/>
-      <c r="T13" s="52"/>
-      <c r="U13" s="47"/>
-      <c r="V13" s="47"/>
-      <c r="W13" s="14"/>
-      <c r="X13" s="14"/>
-      <c r="Y13" s="8"/>
-    </row>
-    <row r="14" spans="1:25" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.4">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="47"/>
-      <c r="G14" s="47"/>
-      <c r="H14" s="47"/>
-      <c r="I14" s="47"/>
-      <c r="J14" s="47"/>
-      <c r="K14" s="47"/>
-      <c r="L14" s="47"/>
-      <c r="M14" s="47"/>
-      <c r="N14" s="47"/>
-      <c r="O14" s="47"/>
-      <c r="P14" s="47"/>
-      <c r="Q14" s="47"/>
-      <c r="R14" s="47"/>
-      <c r="S14" s="51"/>
-      <c r="T14" s="52"/>
-      <c r="U14" s="47"/>
-      <c r="V14" s="47"/>
-      <c r="W14" s="14"/>
-      <c r="X14" s="14"/>
-      <c r="Y14" s="8"/>
-    </row>
-    <row r="15" spans="1:25" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.4">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="47"/>
-      <c r="G15" s="47"/>
-      <c r="H15" s="47"/>
-      <c r="I15" s="47"/>
-      <c r="J15" s="47"/>
-      <c r="K15" s="47"/>
-      <c r="L15" s="47"/>
-      <c r="M15" s="47"/>
-      <c r="N15" s="47"/>
-      <c r="O15" s="47"/>
-      <c r="P15" s="47"/>
-      <c r="Q15" s="47"/>
-      <c r="R15" s="47"/>
-      <c r="S15" s="51"/>
-      <c r="T15" s="52"/>
-      <c r="U15" s="47"/>
-      <c r="V15" s="47"/>
-      <c r="W15" s="14"/>
-      <c r="X15" s="14"/>
-      <c r="Y15" s="8"/>
-    </row>
-    <row r="16" spans="1:25" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="17" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="18" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="19" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4"/>
+      <c r="F12" s="51"/>
+      <c r="G12" s="51"/>
+      <c r="H12" s="51"/>
+      <c r="I12" s="51"/>
+      <c r="J12" s="51"/>
+      <c r="K12" s="51"/>
+      <c r="L12" s="51"/>
+      <c r="M12" s="52"/>
+      <c r="N12" s="53"/>
+      <c r="O12" s="51"/>
+      <c r="P12" s="51"/>
+      <c r="Q12" s="14"/>
+      <c r="R12" s="14"/>
+      <c r="S12" s="8"/>
+    </row>
+    <row r="13" spans="1:19" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="14" spans="1:19" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="15" spans="1:19" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="16" spans="1:19" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
-  <mergeCells count="58">
-    <mergeCell ref="W1:X2"/>
-    <mergeCell ref="W3:X4"/>
-    <mergeCell ref="A1:G4"/>
-    <mergeCell ref="H1:L1"/>
-    <mergeCell ref="M1:S1"/>
-    <mergeCell ref="T1:V2"/>
-    <mergeCell ref="T3:V4"/>
-    <mergeCell ref="M4:S4"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="M2:S2"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="M3:S3"/>
-    <mergeCell ref="H4:L4"/>
-    <mergeCell ref="S8:T8"/>
-    <mergeCell ref="S5:T5"/>
-    <mergeCell ref="U5:V5"/>
+  <mergeCells count="37">
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="I1:O1"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="O6:P6"/>
+    <mergeCell ref="O7:P7"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="O5:P5"/>
     <mergeCell ref="F8:L8"/>
-    <mergeCell ref="M8:R8"/>
-    <mergeCell ref="M5:R5"/>
     <mergeCell ref="F5:L5"/>
-    <mergeCell ref="U8:V8"/>
-    <mergeCell ref="U9:V9"/>
-    <mergeCell ref="S10:T10"/>
-    <mergeCell ref="U10:V10"/>
-    <mergeCell ref="S9:T9"/>
-    <mergeCell ref="F9:L9"/>
-    <mergeCell ref="M9:R9"/>
+    <mergeCell ref="O8:P8"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="P1:R2"/>
+    <mergeCell ref="P3:R4"/>
+    <mergeCell ref="I4:O4"/>
+    <mergeCell ref="I2:O2"/>
+    <mergeCell ref="I3:O3"/>
+    <mergeCell ref="S1:S2"/>
+    <mergeCell ref="S3:S4"/>
     <mergeCell ref="F12:L12"/>
-    <mergeCell ref="M12:R12"/>
-    <mergeCell ref="S12:T12"/>
-    <mergeCell ref="U12:V12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="O12:P12"/>
+    <mergeCell ref="F11:L11"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="O11:P11"/>
     <mergeCell ref="F10:L10"/>
-    <mergeCell ref="M10:R10"/>
-    <mergeCell ref="S11:T11"/>
-    <mergeCell ref="U11:V11"/>
-    <mergeCell ref="F11:L11"/>
-    <mergeCell ref="M11:R11"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="S7:T7"/>
-    <mergeCell ref="U6:V6"/>
-    <mergeCell ref="U7:V7"/>
-    <mergeCell ref="F15:L15"/>
-    <mergeCell ref="M15:R15"/>
-    <mergeCell ref="S15:T15"/>
-    <mergeCell ref="U15:V15"/>
-    <mergeCell ref="F14:L14"/>
-    <mergeCell ref="M14:R14"/>
-    <mergeCell ref="S14:T14"/>
-    <mergeCell ref="U14:V14"/>
-    <mergeCell ref="F13:L13"/>
-    <mergeCell ref="M13:R13"/>
-    <mergeCell ref="S13:T13"/>
-    <mergeCell ref="U13:V13"/>
-    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="O10:P10"/>
     <mergeCell ref="F6:L6"/>
     <mergeCell ref="F7:L7"/>
-    <mergeCell ref="M6:R6"/>
-    <mergeCell ref="M7:R7"/>
+    <mergeCell ref="F9:L9"/>
+    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="O9:P9"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3101,190 +3081,190 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
-      <c r="H1" s="58"/>
-      <c r="I1" s="58"/>
-      <c r="J1" s="58"/>
-      <c r="K1" s="58"/>
-      <c r="L1" s="58"/>
-      <c r="M1" s="58"/>
-      <c r="N1" s="59"/>
-      <c r="O1" s="54" t="s">
+      <c r="B1" s="80"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
+      <c r="F1" s="80"/>
+      <c r="G1" s="80"/>
+      <c r="H1" s="80"/>
+      <c r="I1" s="80"/>
+      <c r="J1" s="80"/>
+      <c r="K1" s="80"/>
+      <c r="L1" s="80"/>
+      <c r="M1" s="80"/>
+      <c r="N1" s="81"/>
+      <c r="O1" s="82" t="s">
         <v>0</v>
       </c>
-      <c r="P1" s="54"/>
-      <c r="Q1" s="54"/>
-      <c r="R1" s="54"/>
-      <c r="S1" s="54"/>
-      <c r="T1" s="55" t="s">
+      <c r="P1" s="82"/>
+      <c r="Q1" s="82"/>
+      <c r="R1" s="82"/>
+      <c r="S1" s="82"/>
+      <c r="T1" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="U1" s="55"/>
-      <c r="V1" s="55"/>
-      <c r="W1" s="55"/>
-      <c r="X1" s="55"/>
-      <c r="Y1" s="55"/>
-      <c r="Z1" s="55"/>
-      <c r="AA1" s="55"/>
-      <c r="AB1" s="66" t="s">
+      <c r="U1" s="56"/>
+      <c r="V1" s="56"/>
+      <c r="W1" s="56"/>
+      <c r="X1" s="56"/>
+      <c r="Y1" s="56"/>
+      <c r="Z1" s="56"/>
+      <c r="AA1" s="56"/>
+      <c r="AB1" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="AC1" s="66"/>
-      <c r="AD1" s="66"/>
-      <c r="AE1" s="76" t="str">
-        <f>試験項目!W1</f>
+      <c r="AC1" s="54"/>
+      <c r="AD1" s="54"/>
+      <c r="AE1" s="83" t="str">
+        <f>試験項目!S1</f>
         <v>佐藤</v>
       </c>
-      <c r="AF1" s="76"/>
-      <c r="AG1" s="76"/>
-      <c r="AH1" s="76"/>
+      <c r="AF1" s="83"/>
+      <c r="AG1" s="83"/>
+      <c r="AH1" s="83"/>
     </row>
     <row r="2" spans="1:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="60"/>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="61"/>
-      <c r="L2" s="61"/>
-      <c r="M2" s="61"/>
-      <c r="N2" s="62"/>
-      <c r="O2" s="54" t="s">
+      <c r="A2" s="63"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
+      <c r="I2" s="64"/>
+      <c r="J2" s="64"/>
+      <c r="K2" s="64"/>
+      <c r="L2" s="64"/>
+      <c r="M2" s="64"/>
+      <c r="N2" s="65"/>
+      <c r="O2" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="P2" s="54"/>
-      <c r="Q2" s="54"/>
-      <c r="R2" s="54"/>
-      <c r="S2" s="54"/>
-      <c r="T2" s="55" t="s">
+      <c r="P2" s="82"/>
+      <c r="Q2" s="82"/>
+      <c r="R2" s="82"/>
+      <c r="S2" s="82"/>
+      <c r="T2" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="U2" s="55"/>
-      <c r="V2" s="55"/>
-      <c r="W2" s="55"/>
-      <c r="X2" s="55"/>
-      <c r="Y2" s="55"/>
-      <c r="Z2" s="55"/>
-      <c r="AA2" s="55"/>
-      <c r="AB2" s="66"/>
-      <c r="AC2" s="66"/>
-      <c r="AD2" s="66"/>
-      <c r="AE2" s="76"/>
-      <c r="AF2" s="76"/>
-      <c r="AG2" s="76"/>
-      <c r="AH2" s="76"/>
+      <c r="U2" s="56"/>
+      <c r="V2" s="56"/>
+      <c r="W2" s="56"/>
+      <c r="X2" s="56"/>
+      <c r="Y2" s="56"/>
+      <c r="Z2" s="56"/>
+      <c r="AA2" s="56"/>
+      <c r="AB2" s="54"/>
+      <c r="AC2" s="54"/>
+      <c r="AD2" s="54"/>
+      <c r="AE2" s="83"/>
+      <c r="AF2" s="83"/>
+      <c r="AG2" s="83"/>
+      <c r="AH2" s="83"/>
     </row>
     <row r="3" spans="1:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="60"/>
-      <c r="B3" s="61"/>
-      <c r="C3" s="61"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="61"/>
-      <c r="H3" s="61"/>
-      <c r="I3" s="61"/>
-      <c r="J3" s="61"/>
-      <c r="K3" s="61"/>
-      <c r="L3" s="61"/>
-      <c r="M3" s="61"/>
-      <c r="N3" s="62"/>
-      <c r="O3" s="54" t="s">
+      <c r="A3" s="63"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="64"/>
+      <c r="K3" s="64"/>
+      <c r="L3" s="64"/>
+      <c r="M3" s="64"/>
+      <c r="N3" s="65"/>
+      <c r="O3" s="82" t="s">
         <v>5</v>
       </c>
-      <c r="P3" s="54"/>
-      <c r="Q3" s="54"/>
-      <c r="R3" s="54"/>
-      <c r="S3" s="54"/>
-      <c r="T3" s="76" t="str">
-        <f>試験項目!M3</f>
+      <c r="P3" s="82"/>
+      <c r="Q3" s="82"/>
+      <c r="R3" s="82"/>
+      <c r="S3" s="82"/>
+      <c r="T3" s="83" t="str">
+        <f>試験項目!I3</f>
         <v>在庫センター情報</v>
       </c>
-      <c r="U3" s="76"/>
-      <c r="V3" s="76"/>
-      <c r="W3" s="76"/>
-      <c r="X3" s="76"/>
-      <c r="Y3" s="76"/>
-      <c r="Z3" s="76"/>
-      <c r="AA3" s="76"/>
-      <c r="AB3" s="66" t="s">
+      <c r="U3" s="83"/>
+      <c r="V3" s="83"/>
+      <c r="W3" s="83"/>
+      <c r="X3" s="83"/>
+      <c r="Y3" s="83"/>
+      <c r="Z3" s="83"/>
+      <c r="AA3" s="83"/>
+      <c r="AB3" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="AC3" s="66"/>
-      <c r="AD3" s="66"/>
-      <c r="AE3" s="74">
-        <f>試験項目!W3</f>
+      <c r="AC3" s="54"/>
+      <c r="AD3" s="54"/>
+      <c r="AE3" s="84">
+        <f>試験項目!S3</f>
         <v>45700</v>
       </c>
-      <c r="AF3" s="75"/>
-      <c r="AG3" s="75"/>
-      <c r="AH3" s="75"/>
+      <c r="AF3" s="85"/>
+      <c r="AG3" s="85"/>
+      <c r="AH3" s="85"/>
     </row>
     <row r="4" spans="1:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="60"/>
-      <c r="B4" s="61"/>
-      <c r="C4" s="61"/>
-      <c r="D4" s="61"/>
-      <c r="E4" s="61"/>
-      <c r="F4" s="61"/>
-      <c r="G4" s="61"/>
-      <c r="H4" s="61"/>
-      <c r="I4" s="61"/>
-      <c r="J4" s="64"/>
-      <c r="K4" s="64"/>
-      <c r="L4" s="64"/>
-      <c r="M4" s="64"/>
-      <c r="N4" s="65"/>
-      <c r="O4" s="54" t="s">
+      <c r="A4" s="63"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="67"/>
+      <c r="K4" s="67"/>
+      <c r="L4" s="67"/>
+      <c r="M4" s="67"/>
+      <c r="N4" s="68"/>
+      <c r="O4" s="82" t="s">
         <v>4</v>
       </c>
-      <c r="P4" s="54"/>
-      <c r="Q4" s="54"/>
-      <c r="R4" s="54"/>
-      <c r="S4" s="54"/>
-      <c r="T4" s="76" t="str">
-        <f>試験項目!M4</f>
+      <c r="P4" s="82"/>
+      <c r="Q4" s="82"/>
+      <c r="R4" s="82"/>
+      <c r="S4" s="82"/>
+      <c r="T4" s="83" t="str">
+        <f>試験項目!I4</f>
         <v>IT01F004</v>
       </c>
-      <c r="U4" s="76"/>
-      <c r="V4" s="76"/>
-      <c r="W4" s="76"/>
-      <c r="X4" s="76"/>
-      <c r="Y4" s="76"/>
-      <c r="Z4" s="76"/>
-      <c r="AA4" s="76"/>
-      <c r="AB4" s="66"/>
-      <c r="AC4" s="66"/>
-      <c r="AD4" s="66"/>
-      <c r="AE4" s="75"/>
-      <c r="AF4" s="75"/>
-      <c r="AG4" s="75"/>
-      <c r="AH4" s="75"/>
+      <c r="U4" s="83"/>
+      <c r="V4" s="83"/>
+      <c r="W4" s="83"/>
+      <c r="X4" s="83"/>
+      <c r="Y4" s="83"/>
+      <c r="Z4" s="83"/>
+      <c r="AA4" s="83"/>
+      <c r="AB4" s="54"/>
+      <c r="AC4" s="54"/>
+      <c r="AD4" s="54"/>
+      <c r="AE4" s="85"/>
+      <c r="AF4" s="85"/>
+      <c r="AG4" s="85"/>
+      <c r="AH4" s="85"/>
     </row>
     <row r="5" spans="1:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="72" t="s">
+      <c r="A5" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="72"/>
-      <c r="C5" s="72"/>
-      <c r="D5" s="73" t="s">
+      <c r="B5" s="77"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="73"/>
-      <c r="F5" s="73"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
@@ -7217,16 +7197,16 @@
       <c r="AW82" s="22"/>
     </row>
     <row r="83" spans="1:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A83" s="70" t="s">
+      <c r="A83" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="B83" s="70"/>
-      <c r="C83" s="70"/>
-      <c r="D83" s="71" t="s">
-        <v>42</v>
-      </c>
-      <c r="E83" s="71"/>
-      <c r="F83" s="71"/>
+      <c r="B83" s="75"/>
+      <c r="C83" s="75"/>
+      <c r="D83" s="76" t="s">
+        <v>31</v>
+      </c>
+      <c r="E83" s="76"/>
+      <c r="F83" s="76"/>
       <c r="G83" s="28"/>
       <c r="H83" s="28"/>
       <c r="I83" s="28"/>
@@ -7629,16 +7609,16 @@
       <c r="AW90" s="22"/>
     </row>
     <row r="91" spans="1:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A91" s="70" t="s">
+      <c r="A91" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="B91" s="70"/>
-      <c r="C91" s="70"/>
-      <c r="D91" s="71" t="s">
-        <v>43</v>
-      </c>
-      <c r="E91" s="71"/>
-      <c r="F91" s="71"/>
+      <c r="B91" s="75"/>
+      <c r="C91" s="75"/>
+      <c r="D91" s="76" t="s">
+        <v>32</v>
+      </c>
+      <c r="E91" s="76"/>
+      <c r="F91" s="76"/>
       <c r="G91" s="28"/>
       <c r="H91" s="28"/>
       <c r="I91" s="28"/>
@@ -7737,7 +7717,7 @@
     <row r="93" spans="1:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="23"/>
       <c r="B93" s="1" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="AW93" s="24"/>
     </row>
@@ -7816,7 +7796,7 @@
     <row r="112" spans="1:49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="23"/>
       <c r="B112" s="1" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="AW112" s="24"/>
     </row>
@@ -8147,7 +8127,7 @@
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="40" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="37" orientation="portrait" r:id="rId1"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="82" max="49" man="1"/>
   </rowBreaks>
@@ -8161,7 +8141,7 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <sheetData/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8180,141 +8160,153 @@
     <col min="5" max="5" width="30.33203125" style="1" customWidth="1"/>
     <col min="6" max="6" width="24.88671875" style="1" customWidth="1"/>
     <col min="7" max="7" width="15.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.21875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="34.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.33203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="34.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="16384" width="3.6640625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="79" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
+      <c r="B1" s="80"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
       <c r="E1" s="31" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="66" t="s">
+      <c r="G1" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="76"/>
+      <c r="H1" s="83" t="str">
+        <f>試験項目!S1</f>
+        <v>佐藤</v>
+      </c>
     </row>
     <row r="2" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="60"/>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
+      <c r="A2" s="63"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
       <c r="E2" s="31" t="s">
         <v>2</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="66"/>
-      <c r="H2" s="76"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="83"/>
     </row>
     <row r="3" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="60"/>
-      <c r="B3" s="61"/>
-      <c r="C3" s="61"/>
-      <c r="D3" s="61"/>
+      <c r="A3" s="63"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
       <c r="E3" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="66" t="s">
+      <c r="F3" s="5" t="str">
+        <f>試験項目!I3</f>
+        <v>在庫センター情報</v>
+      </c>
+      <c r="G3" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="75"/>
+      <c r="H3" s="49">
+        <f>試験項目!S3</f>
+        <v>45700</v>
+      </c>
     </row>
     <row r="4" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="63"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
+      <c r="A4" s="66"/>
+      <c r="B4" s="67"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
       <c r="E4" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="5"/>
-      <c r="G4" s="66"/>
-      <c r="H4" s="75"/>
+      <c r="F4" s="5" t="str">
+        <f>試験項目!I4</f>
+        <v>IT01F004</v>
+      </c>
+      <c r="G4" s="91"/>
+      <c r="H4" s="89"/>
     </row>
     <row r="5" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="54" t="s">
-        <v>61</v>
-      </c>
-      <c r="B5" s="54" t="s">
-        <v>46</v>
-      </c>
-      <c r="C5" s="78" t="s">
-        <v>56</v>
-      </c>
-      <c r="D5" s="77" t="s">
+      <c r="A5" s="82" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" s="82" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="88" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="86" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" s="86" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="86" t="s">
+        <v>41</v>
+      </c>
+      <c r="G5" s="86" t="s">
+        <v>43</v>
+      </c>
+      <c r="H5" s="86" t="s">
+        <v>39</v>
+      </c>
+      <c r="I5" s="82" t="s">
         <v>47</v>
       </c>
-      <c r="E5" s="77" t="s">
-        <v>49</v>
-      </c>
-      <c r="F5" s="77" t="s">
-        <v>52</v>
-      </c>
-      <c r="G5" s="77" t="s">
-        <v>54</v>
-      </c>
-      <c r="H5" s="77" t="s">
-        <v>50</v>
-      </c>
-      <c r="I5" s="54" t="s">
-        <v>58</v>
-      </c>
-      <c r="J5" s="77" t="s">
-        <v>59</v>
+      <c r="J5" s="86" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="77"/>
-      <c r="B6" s="77"/>
-      <c r="C6" s="77"/>
-      <c r="D6" s="79"/>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79"/>
-      <c r="H6" s="79"/>
-      <c r="I6" s="54"/>
-      <c r="J6" s="79"/>
+      <c r="A6" s="86"/>
+      <c r="B6" s="86"/>
+      <c r="C6" s="86"/>
+      <c r="D6" s="87"/>
+      <c r="E6" s="87"/>
+      <c r="F6" s="87"/>
+      <c r="G6" s="87"/>
+      <c r="H6" s="87"/>
+      <c r="I6" s="82"/>
+      <c r="J6" s="87"/>
     </row>
     <row r="7" spans="1:17" ht="100.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="33" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="B7" s="32">
         <v>45700</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="J7" s="34">
         <v>45700</v>
@@ -8428,9 +8420,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C30147F4-02A2-450E-834E-2F708B354339}">
   <dimension ref="A1:AW45"/>
-  <sheetFormatPr defaultColWidth="3.77734375" defaultRowHeight="16.5" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="3.6640625" defaultRowHeight="16.5" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="16384" width="3.77734375" style="41"/>
+    <col min="1" max="16384" width="3.6640625" style="41"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:49" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
@@ -8487,7 +8479,7 @@
     <row r="2" spans="1:49" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="39"/>
       <c r="B2" s="38" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="AW2" s="40"/>
     </row>
@@ -8566,7 +8558,7 @@
     <row r="21" spans="1:49" s="38" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="39"/>
       <c r="B21" s="38" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="AW21" s="40"/>
     </row>
